--- a/corr_matrix/residual_exam4C_1PL.xlsx
+++ b/corr_matrix/residual_exam4C_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4C02</t>
@@ -565,76 +570,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1572052667785191</v>
+        <v>-0.1571840156539474</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1071129772819587</v>
+        <v>0.1071397744287474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1945850253782301</v>
+        <v>0.1945724364530377</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01225612130373325</v>
+        <v>0.01226000287190175</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1141443503279966</v>
+        <v>-0.1141444099797189</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1225671881549304</v>
+        <v>-0.1225692741608353</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08931243148712904</v>
+        <v>0.08929559344546416</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0042468932490363</v>
+        <v>-0.004225619822348092</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06698112601046401</v>
+        <v>0.06696988470831169</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.06326431168225459</v>
+        <v>-0.06327286775540512</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.157058611689967</v>
+        <v>-0.1570307647094013</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1716397863165671</v>
+        <v>-0.1716556208061596</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.03135877285335768</v>
+        <v>-0.0313580046367908</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05091708529918963</v>
+        <v>-0.05091194464499177</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.120918557932249</v>
+        <v>-0.1209195163203637</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.04206762437222959</v>
+        <v>-0.04205827338280313</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1212107470227284</v>
+        <v>-0.1211834092746712</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03187803281490536</v>
+        <v>0.03185604377449275</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0829096380927254</v>
+        <v>-0.08291644934376764</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.203050734314848</v>
+        <v>-0.2030465982120474</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.06665846803367191</v>
+        <v>-0.06666305675669179</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1247636803203111</v>
+        <v>-0.1247699216760937</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1032329632841247</v>
+        <v>-0.1032195943053734</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05866079474404458</v>
+        <v>0.05864754296900707</v>
       </c>
     </row>
     <row r="3">
@@ -644,79 +649,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1572052667785191</v>
+        <v>-0.1571840156539474</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.169130391734607</v>
+        <v>-0.1691119684610267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09778282266507003</v>
+        <v>0.09777853498293329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03622926989770204</v>
+        <v>0.03623726251114363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1060790205193459</v>
+        <v>0.1060787609190666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1018796162800439</v>
+        <v>0.1018793268602131</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04096165048210238</v>
+        <v>0.04095979454045415</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1300515544210453</v>
+        <v>-0.1300360681576248</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.03594482250535842</v>
+        <v>-0.03594827875982536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1200469904316007</v>
+        <v>0.1200412179414903</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09927545014482982</v>
+        <v>0.09927476369691048</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1161994864524008</v>
+        <v>0.1161933608388695</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3116116890942613</v>
+        <v>-0.311627005359685</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08827924910079146</v>
+        <v>-0.08828070426740714</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.01967765429882575</v>
+        <v>-0.01967546299800828</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1253143198556612</v>
+        <v>0.125335150197763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05990170631816507</v>
+        <v>-0.05988634407687725</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08186244948959918</v>
+        <v>-0.08186666210531482</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001674500357840567</v>
+        <v>-0.0016777047188636</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.03739366968432161</v>
+        <v>-0.03740417475970774</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2981424791877836</v>
+        <v>-0.298136732530352</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1849666801226267</v>
+        <v>-0.1849850849763701</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.186587575937782</v>
+        <v>-0.1865766536574357</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1045821812687073</v>
+        <v>-0.1045794064689808</v>
       </c>
     </row>
     <row r="4">
@@ -726,79 +731,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1071129772819587</v>
+        <v>0.1071397744287474</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.169130391734607</v>
+        <v>-0.1691119684610267</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03830515148816602</v>
+        <v>-0.03831449948521755</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0410968790275268</v>
+        <v>-0.04109258914609979</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005120817767788975</v>
+        <v>0.00511489346711046</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2099140218521304</v>
+        <v>-0.2099178846101358</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06125848442359783</v>
+        <v>0.06124632037930655</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1656981301855193</v>
+        <v>-0.1656675372604765</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.02863071930300732</v>
+        <v>-0.02864280108541816</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1200239875047002</v>
+        <v>-0.1200339410005161</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1502889111432278</v>
+        <v>-0.1502715935183645</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09505869596708556</v>
+        <v>-0.09507554946186222</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1288087371235097</v>
+        <v>-0.1288170140653984</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005339735676082193</v>
+        <v>0.005337916261161278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.257172407117804</v>
+        <v>-0.2571758306075616</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01850954270916713</v>
+        <v>0.01852038677858048</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1679840480847823</v>
+        <v>-0.1679613749144513</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0217426537394485</v>
+        <v>-0.02176023719612016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2227097214285613</v>
+        <v>0.222694593489602</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1758913454857224</v>
+        <v>-0.1758866155333893</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04745547593375988</v>
+        <v>0.04745188178678159</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01134218952123268</v>
+        <v>0.01132937731988661</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00445160297730204</v>
+        <v>0.004459328523960319</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.01320507811982867</v>
+        <v>-0.01321412895070736</v>
       </c>
     </row>
     <row r="5">
@@ -808,79 +813,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1945850253782301</v>
+        <v>0.1945724364530377</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09778282266507003</v>
+        <v>0.09777853498293329</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.03830515148816602</v>
+        <v>-0.03831449948521755</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.04110787523253557</v>
+        <v>-0.04110759344026605</v>
       </c>
       <c r="G5" t="n">
-        <v>0.181864915999761</v>
+        <v>0.181868169741407</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1798728198266253</v>
+        <v>0.1798766137378995</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08815725208001868</v>
+        <v>-0.08815407800558642</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08944535911996229</v>
+        <v>0.08943337311480226</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1456851390910689</v>
+        <v>-0.1456787479289059</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.06927083927540389</v>
+        <v>-0.06926517744188923</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.008080909425435974</v>
+        <v>-0.008084637542002475</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1215905024140825</v>
+        <v>-0.1215826795064629</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2670700605652401</v>
+        <v>-0.2670692036378073</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.04810425522746158</v>
+        <v>-0.04810140560526445</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2194853432044248</v>
+        <v>-0.2194839309914153</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0800043403590924</v>
+        <v>0.08000137009267441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1207445227106266</v>
+        <v>-0.1207465234591133</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1268927227325453</v>
+        <v>-0.1268859556469304</v>
       </c>
       <c r="U5" t="n">
-        <v>0.147657393104382</v>
+        <v>0.1476628662321825</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1555926940812194</v>
+        <v>-0.1555946829095703</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1642184177560117</v>
+        <v>-0.1642166047770798</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1897435985159542</v>
+        <v>0.1897536330361292</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1529131342171595</v>
+        <v>-0.1529134597766434</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1533105459598706</v>
+        <v>-0.1533074216388809</v>
       </c>
     </row>
     <row r="6">
@@ -890,79 +895,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01225612130373325</v>
+        <v>0.01226000287190175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03622926989770204</v>
+        <v>0.03623726251114363</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0410968790275268</v>
+        <v>-0.04109258914609979</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.04110787523253557</v>
+        <v>-0.04110759344026605</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09136965425435853</v>
+        <v>-0.09136595246198143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1502069267368949</v>
+        <v>0.1502109919879639</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0806335845521134</v>
+        <v>-0.08063588905996566</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1212267183735251</v>
+        <v>-0.1212321108700596</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.115183738809049</v>
+        <v>-0.1151785280931766</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.04685950091524699</v>
+        <v>-0.04685740620093272</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1635284463726732</v>
+        <v>-0.1635163245040915</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2217806831795582</v>
+        <v>0.2217834668329278</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.03594966294638322</v>
+        <v>-0.03593424627728482</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01832380318363853</v>
+        <v>-0.01832300344391008</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01893742610570766</v>
+        <v>0.01894829642856827</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1250585768434647</v>
+        <v>-0.1250588421587509</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09493675307257177</v>
+        <v>0.09493997211598093</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2612405032726972</v>
+        <v>0.2612409856802076</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1178172723850887</v>
+        <v>-0.1178106966808624</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1265535632906725</v>
+        <v>0.1265590701408163</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1318419009001987</v>
+        <v>-0.1318407642970224</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.06589277328969292</v>
+        <v>-0.06587541603331813</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1115739652291615</v>
+        <v>-0.1115672630503282</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1288266970396831</v>
+        <v>-0.1288282388894991</v>
       </c>
     </row>
     <row r="7">
@@ -972,79 +977,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1141443503279966</v>
+        <v>-0.1141444099797189</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1060790205193459</v>
+        <v>0.1060787609190666</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005120817767788975</v>
+        <v>0.00511489346711046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.181864915999761</v>
+        <v>0.181868169741407</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09136965425435853</v>
+        <v>-0.09136595246198143</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06649149653565331</v>
+        <v>-0.06648782909983865</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1586069588010329</v>
+        <v>-0.158611967225643</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.007858434430846634</v>
+        <v>-0.007866560662054321</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2764912868205215</v>
+        <v>-0.2764882369430367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1061703204771507</v>
+        <v>0.1061758090216875</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05942512915103174</v>
+        <v>0.05943012531802211</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.002730236610031845</v>
+        <v>-0.002729040286915664</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06526918961267091</v>
+        <v>0.06527246971751968</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1084000221684477</v>
+        <v>-0.1083904511488755</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1154397766760322</v>
+        <v>-0.1154412308813102</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01451798779943036</v>
+        <v>-0.014524845390457</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1061029048737872</v>
+        <v>-0.1060978487369542</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2378250209684452</v>
+        <v>-0.2378272971035007</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2306295791540712</v>
+        <v>0.230632536656169</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1094471257185169</v>
+        <v>-0.1094512954366313</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1263796744811275</v>
+        <v>-0.1263843472207311</v>
       </c>
       <c r="X7" t="n">
-        <v>0.149383516446058</v>
+        <v>0.1493896663482302</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2902343964171243</v>
+        <v>-0.2902313449412409</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.06104822218478987</v>
+        <v>-0.0610544319405805</v>
       </c>
     </row>
     <row r="8">
@@ -1054,79 +1059,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1225671881549304</v>
+        <v>-0.1225692741608353</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1018796162800439</v>
+        <v>0.1018793268602131</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2099140218521304</v>
+        <v>-0.2099178846101358</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1798728198266253</v>
+        <v>0.1798766137378995</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1502069267368949</v>
+        <v>0.1502109919879639</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06649149653565331</v>
+        <v>-0.06648782909983865</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1618546498411081</v>
+        <v>-0.1618592931118959</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1137180925664166</v>
+        <v>-0.1137242772649686</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2847536535444487</v>
+        <v>-0.2847509075156605</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1509895034670319</v>
+        <v>-0.1509822026385452</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1748672251301098</v>
+        <v>-0.174862925139252</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.007560674137994505</v>
+        <v>-0.007559125383567584</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2249773448122658</v>
+        <v>-0.2249802115213665</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1134871512246951</v>
+        <v>-0.1134772322466968</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1666629829475833</v>
+        <v>0.166662078581421</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1193973729998538</v>
+        <v>0.1193898051099185</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1145181742064264</v>
+        <v>-0.1145146923803532</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0267831665911817</v>
+        <v>0.02678014805659378</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0518570431869214</v>
+        <v>0.05186003452870026</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004824535668598249</v>
+        <v>0.004821134462565751</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2159714307021292</v>
+        <v>0.2159680840211398</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1402624684653641</v>
+        <v>0.1402656481710081</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.0357201001728601</v>
+        <v>-0.03571972437965529</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.06700979647418008</v>
+        <v>-0.06701591884831409</v>
       </c>
     </row>
     <row r="9">
@@ -1136,79 +1141,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08931243148712904</v>
+        <v>0.08929559344546416</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04096165048210238</v>
+        <v>0.04095979454045415</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06125848442359783</v>
+        <v>0.06124632037930655</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08815725208001868</v>
+        <v>-0.08815407800558642</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0806335845521134</v>
+        <v>-0.08063588905996566</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1586069588010329</v>
+        <v>-0.158611967225643</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1618546498411081</v>
+        <v>-0.1618592931118959</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04670817940071975</v>
+        <v>0.04670249342487241</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2786584464317496</v>
+        <v>0.2786537550705154</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1026917961411197</v>
+        <v>-0.102689361140304</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1962026546704718</v>
+        <v>-0.1962119727787254</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4303537344299264</v>
+        <v>0.4303535055977341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08370792492677151</v>
+        <v>0.08369989746462846</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.09018004043797248</v>
+        <v>-0.09018219038505811</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2328001225903772</v>
+        <v>-0.2328124620601186</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1628485622453176</v>
+        <v>0.1628348422199808</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.149599616825551</v>
+        <v>-0.1496129861204472</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5206657972393899</v>
+        <v>0.5206671642269636</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1811201069640948</v>
+        <v>-0.1811248992203312</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01139956822144008</v>
+        <v>0.01140253167778781</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1928510403290756</v>
+        <v>-0.1928594140209064</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2851283327905609</v>
+        <v>-0.2851425630154251</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1765483951990221</v>
+        <v>-0.1765611111784476</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.358131230446657</v>
+        <v>0.358130298235608</v>
       </c>
     </row>
     <row r="10">
@@ -1218,79 +1223,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0042468932490363</v>
+        <v>-0.004225619822348092</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1300515544210453</v>
+        <v>-0.1300360681576248</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1656981301855193</v>
+        <v>-0.1656675372604765</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08944535911996229</v>
+        <v>0.08943337311480226</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1212267183735251</v>
+        <v>-0.1212321108700596</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007858434430846634</v>
+        <v>-0.007866560662054321</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1137180925664166</v>
+        <v>-0.1137242772649686</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04670817940071975</v>
+        <v>0.04670249342487241</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1334503612857385</v>
+        <v>-0.13345688421603</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.03621689210212319</v>
+        <v>-0.03622856281458427</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1750753954565546</v>
+        <v>0.1750863355431678</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1530691170835197</v>
+        <v>-0.1530768481912207</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04686748131530784</v>
+        <v>-0.04686143970235492</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0308452512616494</v>
+        <v>0.03083118784960477</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1858190182686773</v>
+        <v>-0.185810893893641</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02636921585743254</v>
+        <v>0.02638365594234422</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1377480368787491</v>
+        <v>0.1377531826925256</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2175986668677326</v>
+        <v>-0.2176040341221704</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09726032073250022</v>
+        <v>-0.09726590077777879</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1433938679841366</v>
+        <v>-0.1433799941062317</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2700996240982766</v>
+        <v>-0.2700978347181833</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2559266820441959</v>
+        <v>-0.2559200380074679</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.02978802912218722</v>
+        <v>-0.02977676675246842</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03660840141571473</v>
+        <v>0.03660298932551637</v>
       </c>
     </row>
     <row r="11">
@@ -1300,79 +1305,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06698112601046401</v>
+        <v>0.06696988470831169</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.03594482250535842</v>
+        <v>-0.03594827875982536</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.02863071930300732</v>
+        <v>-0.02864280108541816</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1456851390910689</v>
+        <v>-0.1456787479289059</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.115183738809049</v>
+        <v>-0.1151785280931766</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2764912868205215</v>
+        <v>-0.2764882369430367</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2847536535444487</v>
+        <v>-0.2847509075156605</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2786584464317496</v>
+        <v>0.2786537550705154</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1334503612857385</v>
+        <v>-0.13345688421603</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08816265867503999</v>
+        <v>0.08817014126256158</v>
       </c>
       <c r="M11" t="n">
-        <v>0.139029281082279</v>
+        <v>0.1390260507163538</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02877816777160146</v>
+        <v>-0.02877579083916272</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1655999984342173</v>
+        <v>0.1655958449752195</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08392683400574089</v>
+        <v>0.08393686532313439</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3119155612318249</v>
+        <v>-0.311926100794337</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.05323768810517725</v>
+        <v>-0.05325027897672028</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1464220626494244</v>
+        <v>-0.1464225247336968</v>
       </c>
       <c r="T11" t="n">
-        <v>0.008883703623099757</v>
+        <v>0.008881920780596554</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1525431304840452</v>
+        <v>-0.1525414853995298</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1056014461591364</v>
+        <v>0.1055972348549546</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01375083030153123</v>
+        <v>0.01374444389343506</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.03859203284543441</v>
+        <v>-0.03860032395772439</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06857740162288968</v>
+        <v>0.06857303774381512</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.09257447306969324</v>
+        <v>-0.09258081570975631</v>
       </c>
     </row>
     <row r="12">
@@ -1382,79 +1387,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06326431168225459</v>
+        <v>-0.06327286775540512</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1200469904316007</v>
+        <v>0.1200412179414903</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1200239875047002</v>
+        <v>-0.1200339410005161</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06927083927540389</v>
+        <v>-0.06926517744188923</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04685950091524699</v>
+        <v>-0.04685740620093272</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1061703204771507</v>
+        <v>0.1061758090216875</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1509895034670319</v>
+        <v>-0.1509822026385452</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1026917961411197</v>
+        <v>-0.102689361140304</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.03621689210212319</v>
+        <v>-0.03622856281458427</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08816265867503999</v>
+        <v>0.08817014126256158</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2320294261144082</v>
+        <v>0.232023602377259</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1434053814139069</v>
+        <v>-0.1433960495145393</v>
       </c>
       <c r="O12" t="n">
-        <v>0.274452061613089</v>
+        <v>0.2744588328286324</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.05567578695035423</v>
+        <v>-0.05567005105683</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.05689220385156815</v>
+        <v>-0.05688871409231792</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.195144026701897</v>
+        <v>-0.1951478783287468</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1453917872916357</v>
+        <v>-0.1453915428369231</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1490450344470811</v>
+        <v>-0.1490378731922805</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06731566963844246</v>
+        <v>0.06732335849764788</v>
       </c>
       <c r="V12" t="n">
-        <v>0.06012006061685508</v>
+        <v>0.06011663474758359</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1937393473317703</v>
+        <v>-0.1937365279093009</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03965033272451966</v>
+        <v>0.03965589083212907</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.1844806715206293</v>
+        <v>-0.1844792420247008</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.1792179185198684</v>
+        <v>-0.1792144683350522</v>
       </c>
     </row>
     <row r="13">
@@ -1464,79 +1469,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.157058611689967</v>
+        <v>-0.1570307647094013</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09927545014482982</v>
+        <v>0.09927476369691048</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1502889111432278</v>
+        <v>-0.1502715935183645</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.008080909425435974</v>
+        <v>-0.008084637542002475</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1635284463726732</v>
+        <v>-0.1635163245040915</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05942512915103174</v>
+        <v>0.05943012531802211</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1748672251301098</v>
+        <v>-0.174862925139252</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1962026546704718</v>
+        <v>-0.1962119727787254</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1750753954565546</v>
+        <v>0.1750863355431678</v>
       </c>
       <c r="K13" t="n">
-        <v>0.139029281082279</v>
+        <v>0.1390260507163538</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2320294261144082</v>
+        <v>0.232023602377259</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2093155191225898</v>
+        <v>-0.2093259545934082</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02844208091944667</v>
+        <v>0.02843452685569147</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0534745860591947</v>
+        <v>0.0534849327276023</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2155249613411308</v>
+        <v>-0.2155277637024974</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1111037410651205</v>
+        <v>-0.1110895189490247</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.04406871386056489</v>
+        <v>-0.04404248783348764</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.331380200483826</v>
+        <v>-0.3313920183867217</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1405879095338968</v>
+        <v>-0.1405886830888787</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.08819508264558477</v>
+        <v>-0.08820863000089675</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1205807078183762</v>
+        <v>-0.1205773615448551</v>
       </c>
       <c r="X13" t="n">
-        <v>0.007145976619093679</v>
+        <v>0.007128445503637303</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1040286080872781</v>
+        <v>-0.1040155401860154</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2472147686090217</v>
+        <v>-0.2472178407694808</v>
       </c>
     </row>
     <row r="14">
@@ -1546,79 +1551,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1716397863165671</v>
+        <v>-0.1716556208061596</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1161994864524008</v>
+        <v>0.1161933608388695</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09505869596708556</v>
+        <v>-0.09507554946186222</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1215905024140825</v>
+        <v>-0.1215826795064629</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2217806831795582</v>
+        <v>0.2217834668329278</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.002730236610031845</v>
+        <v>-0.002729040286915664</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.007560674137994505</v>
+        <v>-0.007559125383567584</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4303537344299264</v>
+        <v>0.4303535055977341</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1530691170835197</v>
+        <v>-0.1530768481912207</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02877816777160146</v>
+        <v>-0.02877579083916272</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1434053814139069</v>
+        <v>-0.1433960495145393</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2093155191225898</v>
+        <v>-0.2093259545934082</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09234397647216414</v>
+        <v>0.09233518837091619</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1157777616019178</v>
+        <v>-0.1157708141833627</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1863073453037987</v>
+        <v>0.1862997483078913</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1110183445478114</v>
+        <v>-0.1110332620382805</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.07093952360757132</v>
+        <v>-0.07094966548828339</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4817211472531754</v>
+        <v>0.4817234076205755</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05161777246168837</v>
+        <v>-0.05161613836608957</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05104420828343589</v>
+        <v>0.05104249956475804</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.295355753553617</v>
+        <v>-0.295361360575907</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04875866362612472</v>
+        <v>0.04875045712122333</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1122868663782954</v>
+        <v>-0.1122963799655025</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01377133832380912</v>
+        <v>0.01377066687018982</v>
       </c>
     </row>
     <row r="15">
@@ -1628,79 +1633,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.03135877285335768</v>
+        <v>-0.0313580046367908</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3116116890942613</v>
+        <v>-0.311627005359685</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1288087371235097</v>
+        <v>-0.1288170140653984</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2670700605652401</v>
+        <v>-0.2670692036378073</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03594966294638322</v>
+        <v>-0.03593424627728482</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06526918961267091</v>
+        <v>0.06527246971751968</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2249773448122658</v>
+        <v>-0.2249802115213665</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08370792492677151</v>
+        <v>0.08369989746462846</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04686748131530784</v>
+        <v>-0.04686143970235492</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1655999984342173</v>
+        <v>0.1655958449752195</v>
       </c>
       <c r="L15" t="n">
-        <v>0.274452061613089</v>
+        <v>0.2744588328286324</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02844208091944667</v>
+        <v>0.02843452685569147</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09234397647216414</v>
+        <v>0.09233518837091619</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.05340182605521807</v>
+        <v>0.05342132770518994</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1195921315572289</v>
+        <v>-0.1196170798900235</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2567099787315447</v>
+        <v>-0.2567229458043288</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1346062908494847</v>
+        <v>-0.1345970247636205</v>
       </c>
       <c r="T15" t="n">
-        <v>0.203597740742811</v>
+        <v>0.2035871003768294</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.03872973573804413</v>
+        <v>-0.03873716615236023</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.02973519367826007</v>
+        <v>-0.02975366399085901</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1661886320710702</v>
+        <v>-0.1662010262171954</v>
       </c>
       <c r="X15" t="n">
-        <v>0.227559952723403</v>
+        <v>0.2275294508885239</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.1068305196108297</v>
+        <v>-0.1068370180586807</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.006996470264328665</v>
+        <v>0.006988096133359568</v>
       </c>
     </row>
     <row r="16">
@@ -1710,79 +1715,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.05091708529918963</v>
+        <v>-0.05091194464499177</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.08827924910079146</v>
+        <v>-0.08828070426740714</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005339735676082193</v>
+        <v>0.005337916261161278</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04810425522746158</v>
+        <v>-0.04810140560526445</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01832380318363853</v>
+        <v>-0.01832300344391008</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1084000221684477</v>
+        <v>-0.1083904511488755</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1134871512246951</v>
+        <v>-0.1134772322466968</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09018004043797248</v>
+        <v>-0.09018219038505811</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0308452512616494</v>
+        <v>0.03083118784960477</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08392683400574089</v>
+        <v>0.08393686532313439</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.05567578695035423</v>
+        <v>-0.05567005105683</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0534745860591947</v>
+        <v>0.0534849327276023</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1157777616019178</v>
+        <v>-0.1157708141833627</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05340182605521807</v>
+        <v>0.05342132770518994</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2211350065499078</v>
+        <v>-0.2211212785918193</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1882073239962865</v>
+        <v>0.1882137775770852</v>
       </c>
       <c r="S16" t="n">
-        <v>0.04861052386605694</v>
+        <v>0.04861992540512521</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1258286070299103</v>
+        <v>-0.1258256059071985</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1400077577742819</v>
+        <v>-0.139995036555876</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1072886212126623</v>
+        <v>0.1072837100006142</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1544036740377835</v>
+        <v>-0.154397443936999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.154343894092943</v>
+        <v>-0.1543271810691486</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.01715571024601149</v>
+        <v>0.01716780308207477</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1469592813596896</v>
+        <v>-0.1469574774833446</v>
       </c>
     </row>
     <row r="17">
@@ -1792,79 +1797,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.120918557932249</v>
+        <v>-0.1209195163203637</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.01967765429882575</v>
+        <v>-0.01967546299800828</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.257172407117804</v>
+        <v>-0.2571758306075616</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2194853432044248</v>
+        <v>-0.2194839309914153</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01893742610570766</v>
+        <v>0.01894829642856827</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1154397766760322</v>
+        <v>-0.1154412308813102</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1666629829475833</v>
+        <v>0.166662078581421</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2328001225903772</v>
+        <v>-0.2328124620601186</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1858190182686773</v>
+        <v>-0.185810893893641</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3119155612318249</v>
+        <v>-0.311926100794337</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.05689220385156815</v>
+        <v>-0.05688871409231792</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2155249613411308</v>
+        <v>-0.2155277637024974</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1863073453037987</v>
+        <v>0.1862997483078913</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1195921315572289</v>
+        <v>-0.1196170798900235</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2211350065499078</v>
+        <v>-0.2211212785918193</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.02578529025368744</v>
+        <v>-0.02579998755777166</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.01009533199374361</v>
+        <v>-0.01009180236461903</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06923271284738283</v>
+        <v>0.06922009795931591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08316447679186104</v>
+        <v>0.08315780909827827</v>
       </c>
       <c r="V17" t="n">
-        <v>0.02904640411992686</v>
+        <v>0.02904265485845399</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2281076665666381</v>
+        <v>0.2280983971825365</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1341607421686447</v>
+        <v>0.1341366653451566</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.141625868231421</v>
+        <v>0.1416194428773345</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1001410246867755</v>
+        <v>0.1001299147242464</v>
       </c>
     </row>
     <row r="18">
@@ -1874,79 +1879,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04206762437222959</v>
+        <v>-0.04205827338280313</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1253143198556612</v>
+        <v>0.125335150197763</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01850954270916713</v>
+        <v>0.01852038677858048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0800043403590924</v>
+        <v>0.08000137009267441</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1250585768434647</v>
+        <v>-0.1250588421587509</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.01451798779943036</v>
+        <v>-0.014524845390457</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1193973729998538</v>
+        <v>0.1193898051099185</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1628485622453176</v>
+        <v>0.1628348422199808</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02636921585743254</v>
+        <v>0.02638365594234422</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05323768810517725</v>
+        <v>-0.05325027897672028</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.195144026701897</v>
+        <v>-0.1951478783287468</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1111037410651205</v>
+        <v>-0.1110895189490247</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1110183445478114</v>
+        <v>-0.1110332620382805</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2567099787315447</v>
+        <v>-0.2567229458043288</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1882073239962865</v>
+        <v>0.1882137775770852</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.02578529025368744</v>
+        <v>-0.02579998755777166</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01533028209025824</v>
+        <v>0.01533416897974528</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07817824586257238</v>
+        <v>-0.07819726404839906</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08178622434006556</v>
+        <v>-0.08179772883062045</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2802621557110849</v>
+        <v>-0.2802538413878692</v>
       </c>
       <c r="W18" t="n">
-        <v>0.05344419109830446</v>
+        <v>0.05342716533217251</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2156301250494747</v>
+        <v>-0.2156466352334288</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1450339139403906</v>
+        <v>-0.1450388706537185</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.01158223599918352</v>
+        <v>0.01156249939677577</v>
       </c>
     </row>
     <row r="19">
@@ -1956,79 +1961,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1212107470227284</v>
+        <v>-0.1211834092746712</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.05990170631816507</v>
+        <v>-0.05988634407687725</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1679840480847823</v>
+        <v>-0.1679613749144513</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1207445227106266</v>
+        <v>-0.1207465234591133</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09493675307257177</v>
+        <v>0.09493997211598093</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1061029048737872</v>
+        <v>-0.1060978487369542</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1145181742064264</v>
+        <v>-0.1145146923803532</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.149599616825551</v>
+        <v>-0.1496129861204472</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1377480368787491</v>
+        <v>0.1377531826925256</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1464220626494244</v>
+        <v>-0.1464225247336968</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1453917872916357</v>
+        <v>-0.1453915428369231</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.04406871386056489</v>
+        <v>-0.04404248783348764</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.07093952360757132</v>
+        <v>-0.07094966548828339</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1346062908494847</v>
+        <v>-0.1345970247636205</v>
       </c>
       <c r="P19" t="n">
-        <v>0.04861052386605694</v>
+        <v>0.04861992540512521</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.01009533199374361</v>
+        <v>-0.01009180236461903</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01533028209025824</v>
+        <v>0.01533416897974528</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.04335718145733165</v>
+        <v>-0.04337342289981898</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1658158418228166</v>
+        <v>-0.1658133518003976</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0409502477009913</v>
+        <v>-0.0409493117620687</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0438778095603522</v>
+        <v>-0.04388206609930697</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2091174121207695</v>
+        <v>-0.2091144824680051</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1679786944146816</v>
+        <v>0.1679896550667463</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.04288970727806248</v>
+        <v>0.0428774605318795</v>
       </c>
     </row>
     <row r="20">
@@ -2038,79 +2043,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.03187803281490536</v>
+        <v>0.03185604377449275</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.08186244948959918</v>
+        <v>-0.08186666210531482</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0217426537394485</v>
+        <v>-0.02176023719612016</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1268927227325453</v>
+        <v>-0.1268859556469304</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2612405032726972</v>
+        <v>0.2612409856802076</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2378250209684452</v>
+        <v>-0.2378272971035007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0267831665911817</v>
+        <v>0.02678014805659378</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5206657972393899</v>
+        <v>0.5206671642269636</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2175986668677326</v>
+        <v>-0.2176040341221704</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008883703623099757</v>
+        <v>0.008881920780596554</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1490450344470811</v>
+        <v>-0.1490378731922805</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.331380200483826</v>
+        <v>-0.3313920183867217</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4817211472531754</v>
+        <v>0.4817234076205755</v>
       </c>
       <c r="O20" t="n">
-        <v>0.203597740742811</v>
+        <v>0.2035871003768294</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1258286070299103</v>
+        <v>-0.1258256059071985</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.06923271284738283</v>
+        <v>0.06922009795931591</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.07817824586257238</v>
+        <v>-0.07819726404839906</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.04335718145733165</v>
+        <v>-0.04337342289981898</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2768814343623054</v>
+        <v>-0.276883703821779</v>
       </c>
       <c r="V20" t="n">
-        <v>0.03397900556021929</v>
+        <v>0.03398019914916141</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.029280254840269</v>
+        <v>-0.02928855277779841</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.04560722344213056</v>
+        <v>-0.04561985155498444</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.07872501252035514</v>
+        <v>-0.07873988035038219</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3855132658792684</v>
+        <v>0.3855119778864453</v>
       </c>
     </row>
     <row r="21">
@@ -2120,79 +2125,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0829096380927254</v>
+        <v>-0.08291644934376764</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.001674500357840567</v>
+        <v>-0.0016777047188636</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2227097214285613</v>
+        <v>0.222694593489602</v>
       </c>
       <c r="E21" t="n">
-        <v>0.147657393104382</v>
+        <v>0.1476628662321825</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1178172723850887</v>
+        <v>-0.1178106966808624</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2306295791540712</v>
+        <v>0.230632536656169</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0518570431869214</v>
+        <v>0.05186003452870026</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1811201069640948</v>
+        <v>-0.1811248992203312</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.09726032073250022</v>
+        <v>-0.09726590077777879</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1525431304840452</v>
+        <v>-0.1525414853995298</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06731566963844246</v>
+        <v>0.06732335849764788</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1405879095338968</v>
+        <v>-0.1405886830888787</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.05161777246168837</v>
+        <v>-0.05161613836608957</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.03872973573804413</v>
+        <v>-0.03873716615236023</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1400077577742819</v>
+        <v>-0.139995036555876</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.08316447679186104</v>
+        <v>0.08315780909827827</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.08178622434006556</v>
+        <v>-0.08179772883062045</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1658158418228166</v>
+        <v>-0.1658133518003976</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2768814343623054</v>
+        <v>-0.276883703821779</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1087729904272343</v>
+        <v>-0.1087785923850598</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0176126869004561</v>
+        <v>-0.01761884481075221</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03282604232987304</v>
+        <v>0.03281802468563598</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.2260078312562521</v>
+        <v>-0.2260099960241451</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.09673429620001074</v>
+        <v>0.09672837580153848</v>
       </c>
     </row>
     <row r="22">
@@ -2202,79 +2207,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.203050734314848</v>
+        <v>-0.2030465982120474</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.03739366968432161</v>
+        <v>-0.03740417475970774</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1758913454857224</v>
+        <v>-0.1758866155333893</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1555926940812194</v>
+        <v>-0.1555946829095703</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1265535632906725</v>
+        <v>0.1265590701408163</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1094471257185169</v>
+        <v>-0.1094512954366313</v>
       </c>
       <c r="H22" t="n">
-        <v>0.004824535668598249</v>
+        <v>0.004821134462565751</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01139956822144008</v>
+        <v>0.01140253167778781</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1433938679841366</v>
+        <v>-0.1433799941062317</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1056014461591364</v>
+        <v>0.1055972348549546</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06012006061685508</v>
+        <v>0.06011663474758359</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.08819508264558477</v>
+        <v>-0.08820863000089675</v>
       </c>
       <c r="N22" t="n">
-        <v>0.05104420828343589</v>
+        <v>0.05104249956475804</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.02973519367826007</v>
+        <v>-0.02975366399085901</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1072886212126623</v>
+        <v>0.1072837100006142</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02904640411992686</v>
+        <v>0.02904265485845399</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.2802621557110849</v>
+        <v>-0.2802538413878692</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0409502477009913</v>
+        <v>-0.0409493117620687</v>
       </c>
       <c r="T22" t="n">
-        <v>0.03397900556021929</v>
+        <v>0.03398019914916141</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1087729904272343</v>
+        <v>-0.1087785923850598</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.04190775437969375</v>
+        <v>0.04191277028580547</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1854288774583187</v>
+        <v>-0.1854529075608221</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1020012316661948</v>
+        <v>0.1020030483804103</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.05087615830052358</v>
+        <v>-0.05087276460957856</v>
       </c>
     </row>
     <row r="23">
@@ -2284,79 +2289,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06665846803367191</v>
+        <v>-0.06666305675669179</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2981424791877836</v>
+        <v>-0.298136732530352</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04745547593375988</v>
+        <v>0.04745188178678159</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1642184177560117</v>
+        <v>-0.1642166047770798</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1318419009001987</v>
+        <v>-0.1318407642970224</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1263796744811275</v>
+        <v>-0.1263843472207311</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2159714307021292</v>
+        <v>0.2159680840211398</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1928510403290756</v>
+        <v>-0.1928594140209064</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2700996240982766</v>
+        <v>-0.2700978347181833</v>
       </c>
       <c r="K23" t="n">
-        <v>0.01375083030153123</v>
+        <v>0.01374444389343506</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1937393473317703</v>
+        <v>-0.1937365279093009</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1205807078183762</v>
+        <v>-0.1205773615448551</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.295355753553617</v>
+        <v>-0.295361360575907</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1661886320710702</v>
+        <v>-0.1662010262171954</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1544036740377835</v>
+        <v>-0.154397443936999</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2281076665666381</v>
+        <v>0.2280983971825365</v>
       </c>
       <c r="R23" t="n">
-        <v>0.05344419109830446</v>
+        <v>0.05342716533217251</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0438778095603522</v>
+        <v>-0.04388206609930697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.029280254840269</v>
+        <v>-0.02928855277779841</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0176126869004561</v>
+        <v>-0.01761884481075221</v>
       </c>
       <c r="V23" t="n">
-        <v>0.04190775437969375</v>
+        <v>0.04191277028580547</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1870459257999332</v>
+        <v>0.1870437954757584</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.2906124482849416</v>
+        <v>0.2906059769983175</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.08360511457694912</v>
+        <v>0.08359277097902984</v>
       </c>
     </row>
     <row r="24">
@@ -2366,79 +2371,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1247636803203111</v>
+        <v>-0.1247699216760937</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1849666801226267</v>
+        <v>-0.1849850849763701</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01134218952123268</v>
+        <v>0.01132937731988661</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1897435985159542</v>
+        <v>0.1897536330361292</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.06589277328969292</v>
+        <v>-0.06587541603331813</v>
       </c>
       <c r="G24" t="n">
-        <v>0.149383516446058</v>
+        <v>0.1493896663482302</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1402624684653641</v>
+        <v>0.1402656481710081</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2851283327905609</v>
+        <v>-0.2851425630154251</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2559266820441959</v>
+        <v>-0.2559200380074679</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.03859203284543441</v>
+        <v>-0.03860032395772439</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03965033272451966</v>
+        <v>0.03965589083212907</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007145976619093679</v>
+        <v>0.007128445503637303</v>
       </c>
       <c r="N24" t="n">
-        <v>0.04875866362612472</v>
+        <v>0.04875045712122333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.227559952723403</v>
+        <v>0.2275294508885239</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.154343894092943</v>
+        <v>-0.1543271810691486</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1341607421686447</v>
+        <v>0.1341366653451566</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.2156301250494747</v>
+        <v>-0.2156466352334288</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2091174121207695</v>
+        <v>-0.2091144824680051</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.04560722344213056</v>
+        <v>-0.04561985155498444</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03282604232987304</v>
+        <v>0.03281802468563598</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1854288774583187</v>
+        <v>-0.1854529075608221</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1870459257999332</v>
+        <v>0.1870437954757584</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.0826337892253706</v>
+        <v>-0.08264622654163313</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.2116939720274309</v>
+        <v>-0.2117068534667601</v>
       </c>
     </row>
     <row r="25">
@@ -2448,79 +2453,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1032329632841247</v>
+        <v>-0.1032195943053734</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.186587575937782</v>
+        <v>-0.1865766536574357</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00445160297730204</v>
+        <v>0.004459328523960319</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1529131342171595</v>
+        <v>-0.1529134597766434</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1115739652291615</v>
+        <v>-0.1115672630503282</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2902343964171243</v>
+        <v>-0.2902313449412409</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0357201001728601</v>
+        <v>-0.03571972437965529</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1765483951990221</v>
+        <v>-0.1765611111784476</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.02978802912218722</v>
+        <v>-0.02977676675246842</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06857740162288968</v>
+        <v>0.06857303774381512</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1844806715206293</v>
+        <v>-0.1844792420247008</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1040286080872781</v>
+        <v>-0.1040155401860154</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1122868663782954</v>
+        <v>-0.1122963799655025</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1068305196108297</v>
+        <v>-0.1068370180586807</v>
       </c>
       <c r="P25" t="n">
-        <v>0.01715571024601149</v>
+        <v>0.01716780308207477</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.141625868231421</v>
+        <v>0.1416194428773345</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1450339139403906</v>
+        <v>-0.1450388706537185</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1679786944146816</v>
+        <v>0.1679896550667463</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07872501252035514</v>
+        <v>-0.07873988035038219</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2260078312562521</v>
+        <v>-0.2260099960241451</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1020012316661948</v>
+        <v>0.1020030483804103</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2906124482849416</v>
+        <v>0.2906059769983175</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.0826337892253706</v>
+        <v>-0.08264622654163313</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.1578555258071216</v>
+        <v>-0.1578680877103847</v>
       </c>
     </row>
     <row r="26">
@@ -2530,76 +2535,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.05866079474404458</v>
+        <v>0.05864754296900707</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1045821812687073</v>
+        <v>-0.1045794064689808</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.01320507811982867</v>
+        <v>-0.01321412895070736</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1533105459598706</v>
+        <v>-0.1533074216388809</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1288266970396831</v>
+        <v>-0.1288282388894991</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.06104822218478987</v>
+        <v>-0.0610544319405805</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.06700979647418008</v>
+        <v>-0.06701591884831409</v>
       </c>
       <c r="I26" t="n">
-        <v>0.358131230446657</v>
+        <v>0.358130298235608</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03660840141571473</v>
+        <v>0.03660298932551637</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.09257447306969324</v>
+        <v>-0.09258081570975631</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.1792179185198684</v>
+        <v>-0.1792144683350522</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2472147686090217</v>
+        <v>-0.2472178407694808</v>
       </c>
       <c r="N26" t="n">
-        <v>0.01377133832380912</v>
+        <v>0.01377066687018982</v>
       </c>
       <c r="O26" t="n">
-        <v>0.006996470264328665</v>
+        <v>0.006988096133359568</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1469592813596896</v>
+        <v>-0.1469574774833446</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1001410246867755</v>
+        <v>0.1001299147242464</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01158223599918352</v>
+        <v>0.01156249939677577</v>
       </c>
       <c r="S26" t="n">
-        <v>0.04288970727806248</v>
+        <v>0.0428774605318795</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3855132658792684</v>
+        <v>0.3855119778864453</v>
       </c>
       <c r="U26" t="n">
-        <v>0.09673429620001074</v>
+        <v>0.09672837580153848</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.05087615830052358</v>
+        <v>-0.05087276460957856</v>
       </c>
       <c r="W26" t="n">
-        <v>0.08360511457694912</v>
+        <v>0.08359277097902984</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2116939720274309</v>
+        <v>-0.2117068534667601</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.1578555258071216</v>
+        <v>-0.1578680877103847</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>

--- a/corr_matrix/residual_exam4C_1PL.xlsx
+++ b/corr_matrix/residual_exam4C_1PL.xlsx
@@ -1,37 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+  <si>
+    <t>4C02</t>
+  </si>
+  <si>
+    <t>4C03</t>
+  </si>
+  <si>
+    <t>4C04</t>
+  </si>
+  <si>
+    <t>4C05</t>
+  </si>
+  <si>
+    <t>4C06</t>
+  </si>
+  <si>
+    <t>4C07</t>
+  </si>
+  <si>
+    <t>4C08</t>
+  </si>
+  <si>
+    <t>4C09</t>
+  </si>
+  <si>
+    <t>4C10</t>
+  </si>
+  <si>
+    <t>4C11</t>
+  </si>
+  <si>
+    <t>4C12</t>
+  </si>
+  <si>
+    <t>4C13</t>
+  </si>
+  <si>
+    <t>4C14</t>
+  </si>
+  <si>
+    <t>4C15</t>
+  </si>
+  <si>
+    <t>4C16</t>
+  </si>
+  <si>
+    <t>4C17</t>
+  </si>
+  <si>
+    <t>4C18</t>
+  </si>
+  <si>
+    <t>4C19</t>
+  </si>
+  <si>
+    <t>4C20</t>
+  </si>
+  <si>
+    <t>4C21</t>
+  </si>
+  <si>
+    <t>4C22</t>
+  </si>
+  <si>
+    <t>4C23</t>
+  </si>
+  <si>
+    <t>4C24</t>
+  </si>
+  <si>
+    <t>4C25</t>
+  </si>
+  <si>
+    <t>4C26</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +132,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,2197 +448,2091 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>question_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>4C02</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>4C03</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>4C04</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>4C05</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>4C06</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>4C07</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>4C08</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>4C09</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>4C10</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>4C11</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>4C12</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>4C13</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>4C14</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>4C15</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>4C16</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>4C17</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>4C18</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>4C19</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>4C20</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>4C21</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>4C22</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>4C23</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>4C24</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>4C25</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>4C26</t>
-        </is>
+    <row r="1" spans="1:26">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>4C02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:26">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>-0.1571840156539474</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.1071397744287474</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.1945724364530377</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.01226000287190175</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>-0.1141444099797189</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>-0.1225692741608353</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.08929559344546416</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>-0.004225619822348092</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.06696988470831169</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>-0.06327286775540512</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>-0.1570307647094013</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>-0.1716556208061596</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>-0.0313580046367908</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>-0.05091194464499177</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>-0.1209195163203637</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>-0.04205827338280313</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>-0.1211834092746712</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>0.03185604377449275</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>-0.08291644934376764</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>-0.2030465982120474</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2">
         <v>-0.06666305675669179</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2">
         <v>-0.1247699216760937</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2">
         <v>-0.1032195943053734</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>0.05864754296900707</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>4C03</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:26">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>-0.1571840156539474</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>-0.1691119684610267</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.09777853498293329</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.03623726251114363</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.1060787609190666</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.1018793268602131</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.04095979454045415</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>-0.1300360681576248</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>-0.03594827875982536</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.1200412179414903</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.09927476369691048</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.1161933608388695</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>-0.311627005359685</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>-0.08828070426740714</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>-0.01967546299800828</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>0.125335150197763</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>-0.05988634407687725</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>-0.08186666210531482</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>-0.0016777047188636</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>-0.03740417475970774</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3">
         <v>-0.298136732530352</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3">
         <v>-0.1849850849763701</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3">
         <v>-0.1865766536574357</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>-0.1045794064689808</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4C04</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:26">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>0.1071397744287474</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>-0.1691119684610267</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>-0.03831449948521755</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>-0.04109258914609979</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.00511489346711046</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>-0.2099178846101358</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.06124632037930655</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>-0.1656675372604765</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>-0.02864280108541816</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>-0.1200339410005161</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>-0.1502715935183645</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>-0.09507554946186222</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>-0.1288170140653984</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>0.005337916261161278</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>-0.2571758306075616</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>0.01852038677858048</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4">
         <v>-0.1679613749144513</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>-0.02176023719612016</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>0.222694593489602</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>-0.1758866155333893</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4">
         <v>0.04745188178678159</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4">
         <v>0.01132937731988661</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4">
         <v>0.004459328523960319</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4">
         <v>-0.01321412895070736</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>4C05</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:26">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>0.1945724364530377</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.09777853498293329</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>-0.03831449948521755</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>-0.04110759344026605</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.181868169741407</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.1798766137378995</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>-0.08815407800558642</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.08943337311480226</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>-0.1456787479289059</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>-0.06926517744188923</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>-0.008084637542002475</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>-0.1215826795064629</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>-0.2670692036378073</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>-0.04810140560526445</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>-0.2194839309914153</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>0.08000137009267441</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5">
         <v>-0.1207465234591133</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>-0.1268859556469304</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>0.1476628662321825</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>-0.1555946829095703</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5">
         <v>-0.1642166047770798</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5">
         <v>0.1897536330361292</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5">
         <v>-0.1529134597766434</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5">
         <v>-0.1533074216388809</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>4C06</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:26">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>0.01226000287190175</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.03623726251114363</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>-0.04109258914609979</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-0.04110759344026605</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>-0.09136595246198143</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.1502109919879639</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>-0.08063588905996566</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>-0.1212321108700596</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>-0.1151785280931766</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>-0.04685740620093272</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>-0.1635163245040915</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.2217834668329278</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>-0.03593424627728482</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>-0.01832300344391008</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>0.01894829642856827</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>-0.1250588421587509</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6">
         <v>0.09493997211598093</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>0.2612409856802076</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6">
         <v>-0.1178106966808624</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6">
         <v>0.1265590701408163</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6">
         <v>-0.1318407642970224</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6">
         <v>-0.06587541603331813</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6">
         <v>-0.1115672630503282</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z6">
         <v>-0.1288282388894991</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4C07</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:26">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>-0.1141444099797189</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.1060787609190666</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.00511489346711046</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.181868169741407</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>-0.09136595246198143</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>-0.06648782909983865</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>-0.158611967225643</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>-0.007866560662054321</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>-0.2764882369430367</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.1061758090216875</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.05943012531802211</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>-0.002729040286915664</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.06527246971751968</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>-0.1083904511488755</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>-0.1154412308813102</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>-0.014524845390457</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7">
         <v>-0.1060978487369542</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>-0.2378272971035007</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>0.230632536656169</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>-0.1094512954366313</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7">
         <v>-0.1263843472207311</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7">
         <v>0.1493896663482302</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7">
         <v>-0.2902313449412409</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7">
         <v>-0.0610544319405805</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4C08</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:26">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>-0.1225692741608353</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.1018793268602131</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>-0.2099178846101358</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.1798766137378995</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.1502109919879639</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>-0.06648782909983865</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>-0.1618592931118959</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>-0.1137242772649686</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>-0.2847509075156605</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>-0.1509822026385452</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>-0.174862925139252</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>-0.007559125383567584</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>-0.2249802115213665</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>-0.1134772322466968</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>0.166662078581421</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8">
         <v>0.1193898051099185</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8">
         <v>-0.1145146923803532</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8">
         <v>0.02678014805659378</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8">
         <v>0.05186003452870026</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>0.004821134462565751</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W8">
         <v>0.2159680840211398</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X8">
         <v>0.1402656481710081</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y8">
         <v>-0.03571972437965529</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z8">
         <v>-0.06701591884831409</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4C09</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:26">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>0.08929559344546416</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.04095979454045415</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.06124632037930655</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>-0.08815407800558642</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>-0.08063588905996566</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>-0.158611967225643</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>-0.1618592931118959</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>0.04670249342487241</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.2786537550705154</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>-0.102689361140304</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>-0.1962119727787254</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>0.4303535055977341</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.08369989746462846</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>-0.09018219038505811</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>-0.2328124620601186</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9">
         <v>0.1628348422199808</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9">
         <v>-0.1496129861204472</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9">
         <v>0.5206671642269636</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9">
         <v>-0.1811248992203312</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9">
         <v>0.01140253167778781</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W9">
         <v>-0.1928594140209064</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9">
         <v>-0.2851425630154251</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9">
         <v>-0.1765611111784476</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9">
         <v>0.358130298235608</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>4C10</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:26">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
         <v>-0.004225619822348092</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>-0.1300360681576248</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>-0.1656675372604765</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.08943337311480226</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>-0.1212321108700596</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>-0.007866560662054321</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>-0.1137242772649686</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>0.04670249342487241</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
         <v>-0.13345688421603</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>-0.03622856281458427</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.1750863355431678</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>-0.1530768481912207</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>-0.04686143970235492</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>0.03083118784960477</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>-0.185810893893641</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>0.02638365594234422</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10">
         <v>0.1377531826925256</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10">
         <v>-0.2176040341221704</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10">
         <v>-0.09726590077777879</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10">
         <v>-0.1433799941062317</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10">
         <v>-0.2700978347181833</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10">
         <v>-0.2559200380074679</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10">
         <v>-0.02977676675246842</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10">
         <v>0.03660298932551637</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4C11</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:26">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
         <v>0.06696988470831169</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>-0.03594827875982536</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>-0.02864280108541816</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>-0.1456787479289059</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>-0.1151785280931766</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>-0.2764882369430367</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>-0.2847509075156605</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>0.2786537550705154</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>-0.13345688421603</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>0.08817014126256158</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.1390260507163538</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>-0.02877579083916272</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>0.1655958449752195</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>0.08393686532313439</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>-0.311926100794337</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11">
         <v>-0.05325027897672028</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11">
         <v>-0.1464225247336968</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>0.008881920780596554</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11">
         <v>-0.1525414853995298</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11">
         <v>0.1055972348549546</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W11">
         <v>0.01374444389343506</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X11">
         <v>-0.03860032395772439</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11">
         <v>0.06857303774381512</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>-0.09258081570975631</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>4C12</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:26">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
         <v>-0.06327286775540512</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.1200412179414903</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>-0.1200339410005161</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>-0.06926517744188923</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>-0.04685740620093272</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.1061758090216875</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>-0.1509822026385452</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>-0.102689361140304</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>-0.03622856281458427</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.08817014126256158</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
         <v>0.232023602377259</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>-0.1433960495145393</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>0.2744588328286324</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>-0.05567005105683</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>-0.05688871409231792</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>-0.1951478783287468</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12">
         <v>-0.1453915428369231</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>-0.1490378731922805</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12">
         <v>0.06732335849764788</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12">
         <v>0.06011663474758359</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W12">
         <v>-0.1937365279093009</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12">
         <v>0.03965589083212907</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12">
         <v>-0.1844792420247008</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>-0.1792144683350522</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4C13</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:26">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>-0.1570307647094013</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.09927476369691048</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>-0.1502715935183645</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>-0.008084637542002475</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>-0.1635163245040915</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.05943012531802211</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>-0.174862925139252</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>-0.1962119727787254</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>0.1750863355431678</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>0.1390260507163538</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>0.232023602377259</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>-0.2093259545934082</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>0.02843452685569147</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>0.0534849327276023</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>-0.2155277637024974</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13">
         <v>-0.1110895189490247</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13">
         <v>-0.04404248783348764</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13">
         <v>-0.3313920183867217</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13">
         <v>-0.1405886830888787</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13">
         <v>-0.08820863000089675</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W13">
         <v>-0.1205773615448551</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X13">
         <v>0.007128445503637303</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13">
         <v>-0.1040155401860154</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z13">
         <v>-0.2472178407694808</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4C14</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:26">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
         <v>-0.1716556208061596</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.1161933608388695</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>-0.09507554946186222</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>-0.1215826795064629</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.2217834668329278</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>-0.002729040286915664</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>-0.007559125383567584</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.4303535055977341</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>-0.1530768481912207</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>-0.02877579083916272</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>-0.1433960495145393</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>-0.2093259545934082</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
         <v>0.09233518837091619</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>-0.1157708141833627</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>0.1862997483078913</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14">
         <v>-0.1110332620382805</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14">
         <v>-0.07094966548828339</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14">
         <v>0.4817234076205755</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14">
         <v>-0.05161613836608957</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14">
         <v>0.05104249956475804</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W14">
         <v>-0.295361360575907</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X14">
         <v>0.04875045712122333</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14">
         <v>-0.1122963799655025</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z14">
         <v>0.01377066687018982</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4C15</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:26">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <v>-0.0313580046367908</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>-0.311627005359685</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>-0.1288170140653984</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>-0.2670692036378073</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>-0.03593424627728482</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.06527246971751968</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>-0.2249802115213665</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.08369989746462846</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>-0.04686143970235492</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>0.1655958449752195</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>0.2744588328286324</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>0.02843452685569147</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.09233518837091619</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>0.05342132770518994</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>-0.1196170798900235</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>-0.2567229458043288</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15">
         <v>-0.1345970247636205</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15">
         <v>0.2035871003768294</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15">
         <v>-0.03873716615236023</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15">
         <v>-0.02975366399085901</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W15">
         <v>-0.1662010262171954</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X15">
         <v>0.2275294508885239</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15">
         <v>-0.1068370180586807</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z15">
         <v>0.006988096133359568</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4C16</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:26">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
         <v>-0.05091194464499177</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>-0.08828070426740714</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.005337916261161278</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>-0.04810140560526445</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>-0.01832300344391008</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>-0.1083904511488755</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>-0.1134772322466968</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>-0.09018219038505811</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.03083118784960477</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>0.08393686532313439</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>-0.05567005105683</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>0.0534849327276023</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>-0.1157708141833627</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>0.05342132770518994</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
         <v>-0.2211212785918193</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16">
         <v>0.1882137775770852</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16">
         <v>0.04861992540512521</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16">
         <v>-0.1258256059071985</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U16">
         <v>-0.139995036555876</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16">
         <v>0.1072837100006142</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W16">
         <v>-0.154397443936999</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X16">
         <v>-0.1543271810691486</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16">
         <v>0.01716780308207477</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z16">
         <v>-0.1469574774833446</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4C17</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:26">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>-0.1209195163203637</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>-0.01967546299800828</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>-0.2571758306075616</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>-0.2194839309914153</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.01894829642856827</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>-0.1154412308813102</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.166662078581421</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>-0.2328124620601186</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>-0.185810893893641</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>-0.311926100794337</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>-0.05688871409231792</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>-0.2155277637024974</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>0.1862997483078913</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>-0.1196170798900235</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>-0.2211212785918193</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
         <v>-0.02579998755777166</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17">
         <v>-0.01009180236461903</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17">
         <v>0.06922009795931591</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17">
         <v>0.08315780909827827</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17">
         <v>0.02904265485845399</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W17">
         <v>0.2280983971825365</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X17">
         <v>0.1341366653451566</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17">
         <v>0.1416194428773345</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z17">
         <v>0.1001299147242464</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4C18</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:26">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
         <v>-0.04205827338280313</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.125335150197763</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.01852038677858048</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.08000137009267441</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>-0.1250588421587509</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>-0.014524845390457</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>0.1193898051099185</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>0.1628348422199808</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>0.02638365594234422</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>-0.05325027897672028</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>-0.1951478783287468</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>-0.1110895189490247</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>-0.1110332620382805</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>-0.2567229458043288</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>0.1882137775770852</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>-0.02579998755777166</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
         <v>0.01533416897974528</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18">
         <v>-0.07819726404839906</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18">
         <v>-0.08179772883062045</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18">
         <v>-0.2802538413878692</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W18">
         <v>0.05342716533217251</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X18">
         <v>-0.2156466352334288</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18">
         <v>-0.1450388706537185</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18">
         <v>0.01156249939677577</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4C19</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:26">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19">
         <v>-0.1211834092746712</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>-0.05988634407687725</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>-0.1679613749144513</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>-0.1207465234591133</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.09493997211598093</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>-0.1060978487369542</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>-0.1145146923803532</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>-0.1496129861204472</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.1377531826925256</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>-0.1464225247336968</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>-0.1453915428369231</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>-0.04404248783348764</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>-0.07094966548828339</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>-0.1345970247636205</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>0.04861992540512521</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>-0.01009180236461903</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19">
         <v>0.01533416897974528</v>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
         <v>-0.04337342289981898</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U19">
         <v>-0.1658133518003976</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19">
         <v>-0.0409493117620687</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W19">
         <v>-0.04388206609930697</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X19">
         <v>-0.2091144824680051</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19">
         <v>0.1679896550667463</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z19">
         <v>0.0428774605318795</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>4C20</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:26">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
         <v>0.03185604377449275</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>-0.08186666210531482</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>-0.02176023719612016</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>-0.1268859556469304</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.2612409856802076</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>-0.2378272971035007</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>0.02678014805659378</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>0.5206671642269636</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>-0.2176040341221704</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>0.008881920780596554</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>-0.1490378731922805</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>-0.3313920183867217</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>0.4817234076205755</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>0.2035871003768294</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>-0.1258256059071985</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>0.06922009795931591</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20">
         <v>-0.07819726404839906</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20">
         <v>-0.04337342289981898</v>
       </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
         <v>-0.276883703821779</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20">
         <v>0.03398019914916141</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W20">
         <v>-0.02928855277779841</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X20">
         <v>-0.04561985155498444</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20">
         <v>-0.07873988035038219</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z20">
         <v>0.3855119778864453</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>4C21</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:26">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
         <v>-0.08291644934376764</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>-0.0016777047188636</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.222694593489602</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.1476628662321825</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>-0.1178106966808624</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.230632536656169</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.05186003452870026</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>-0.1811248992203312</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>-0.09726590077777879</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>-0.1525414853995298</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>0.06732335849764788</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>-0.1405886830888787</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>-0.05161613836608957</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>-0.03873716615236023</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>-0.139995036555876</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>0.08315780909827827</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21">
         <v>-0.08179772883062045</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21">
         <v>-0.1658133518003976</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21">
         <v>-0.276883703821779</v>
       </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
         <v>-0.1087785923850598</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W21">
         <v>-0.01761884481075221</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X21">
         <v>0.03281802468563598</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21">
         <v>-0.2260099960241451</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z21">
         <v>0.09672837580153848</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>4C22</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:26">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
         <v>-0.2030465982120474</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>-0.03740417475970774</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>-0.1758866155333893</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>-0.1555946829095703</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.1265590701408163</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>-0.1094512954366313</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>0.004821134462565751</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.01140253167778781</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>-0.1433799941062317</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>0.1055972348549546</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>0.06011663474758359</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>-0.08820863000089675</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22">
         <v>0.05104249956475804</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22">
         <v>-0.02975366399085901</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>0.1072837100006142</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>0.02904265485845399</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22">
         <v>-0.2802538413878692</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22">
         <v>-0.0409493117620687</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22">
         <v>0.03398019914916141</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U22">
         <v>-0.1087785923850598</v>
       </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
         <v>0.04191277028580547</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X22">
         <v>-0.1854529075608221</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22">
         <v>0.1020030483804103</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z22">
         <v>-0.05087276460957856</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4C23</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:26">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
         <v>-0.06666305675669179</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>-0.298136732530352</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.04745188178678159</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>-0.1642166047770798</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>-0.1318407642970224</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>-0.1263843472207311</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.2159680840211398</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>-0.1928594140209064</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>-0.2700978347181833</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>0.01374444389343506</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>-0.1937365279093009</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>-0.1205773615448551</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>-0.295361360575907</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>-0.1662010262171954</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>-0.154397443936999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>0.2280983971825365</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23">
         <v>0.05342716533217251</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23">
         <v>-0.04388206609930697</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23">
         <v>-0.02928855277779841</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23">
         <v>-0.01761884481075221</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23">
         <v>0.04191277028580547</v>
       </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
         <v>0.1870437954757584</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23">
         <v>0.2906059769983175</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z23">
         <v>0.08359277097902984</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>4C24</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:26">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24">
         <v>-0.1247699216760937</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>-0.1849850849763701</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.01132937731988661</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.1897536330361292</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>-0.06587541603331813</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.1493896663482302</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>0.1402656481710081</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>-0.2851425630154251</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>-0.2559200380074679</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>-0.03860032395772439</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>0.03965589083212907</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>0.007128445503637303</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24">
         <v>0.04875045712122333</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24">
         <v>0.2275294508885239</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>-0.1543271810691486</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>0.1341366653451566</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24">
         <v>-0.2156466352334288</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24">
         <v>-0.2091144824680051</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24">
         <v>-0.04561985155498444</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U24">
         <v>0.03281802468563598</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V24">
         <v>-0.1854529075608221</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W24">
         <v>0.1870437954757584</v>
       </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
         <v>-0.08264622654163313</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z24">
         <v>-0.2117068534667601</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>4C25</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:26">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25">
         <v>-0.1032195943053734</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>-0.1865766536574357</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.004459328523960319</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>-0.1529134597766434</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>-0.1115672630503282</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>-0.2902313449412409</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>-0.03571972437965529</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>-0.1765611111784476</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>-0.02977676675246842</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>0.06857303774381512</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>-0.1844792420247008</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>-0.1040155401860154</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>-0.1122963799655025</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>-0.1068370180586807</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25">
         <v>0.01716780308207477</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>0.1416194428773345</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25">
         <v>-0.1450388706537185</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25">
         <v>0.1679896550667463</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T25">
         <v>-0.07873988035038219</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U25">
         <v>-0.2260099960241451</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25">
         <v>0.1020030483804103</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W25">
         <v>0.2906059769983175</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X25">
         <v>-0.08264622654163313</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
         <v>-0.1578680877103847</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>4C26</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:26">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26">
         <v>0.05864754296900707</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>-0.1045794064689808</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>-0.01321412895070736</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>-0.1533074216388809</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>-0.1288282388894991</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>-0.0610544319405805</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>-0.06701591884831409</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>0.358130298235608</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>0.03660298932551637</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>-0.09258081570975631</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>-0.1792144683350522</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>-0.2472178407694808</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26">
         <v>0.01377066687018982</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26">
         <v>0.006988096133359568</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26">
         <v>-0.1469574774833446</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26">
         <v>0.1001299147242464</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R26">
         <v>0.01156249939677577</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26">
         <v>0.0428774605318795</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T26">
         <v>0.3855119778864453</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26">
         <v>0.09672837580153848</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26">
         <v>-0.05087276460957856</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W26">
         <v>0.08359277097902984</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X26">
         <v>-0.2117068534667601</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y26">
         <v>-0.1578680877103847</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z26">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>